--- a/excels/英雄表.xlsx
+++ b/excels/英雄表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="128">
   <si>
     <t>主键</t>
   </si>
@@ -132,6 +132,9 @@
   </si>
   <si>
     <t>魔法值</t>
+  </si>
+  <si>
+    <t>初始魔法值</t>
   </si>
   <si>
     <t>生命回复</t>
@@ -322,6 +325,96 @@
   </si>
   <si>
     <t>models/heroes/</t>
+  </si>
+  <si>
+    <t>DOTA_UNIT_CAP_RANGED_ATTACK</t>
+  </si>
+  <si>
+    <t>DOTA_UNIT_CAP_MOVE_GROUND</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 格雷福斯</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 卢锡安</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 慎</t>
+  </si>
+  <si>
+    <t>DOTA_UNIT_CAP_MELEE_ATTACK</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 普朗克</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 金克丝</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 厄运小姐</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 薇恩</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 崔斯特</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 韦鲁斯</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 艾希</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 千珏</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 卡莎</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 伊莉丝</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 莫甘娜</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 伊芙琳</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 布兰德</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 斯维因</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 盖伦</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 菲奥娜</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 蕾欧娜</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 布隆</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 凯尔</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 丽桑卓</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 波比</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 雷克塞</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 科加斯</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 亚索</t>
   </si>
 </sst>
 </file>
@@ -334,14 +427,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -494,7 +580,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -593,12 +679,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -612,12 +692,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -641,12 +715,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -660,12 +728,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -708,12 +770,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -848,152 +904,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1007,6 +1063,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1327,8 +1386,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AN4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3"/>
+  <dimension ref="A1:AO31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20.5666666666667" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.6416666666667" style="1" customWidth="1"/>
@@ -1350,16 +1409,18 @@
     <col min="25" max="30" width="9.14166666666667" style="5" hidden="1" customWidth="1"/>
     <col min="31" max="31" width="42.0833333333333" style="6" customWidth="1"/>
     <col min="32" max="33" width="9.14166666666667" style="6"/>
-    <col min="34" max="36" width="9.14166666666667" style="2"/>
-    <col min="37" max="37" width="16.5" style="2" customWidth="1"/>
-    <col min="38" max="38" width="17.75" style="1" customWidth="1"/>
-    <col min="39" max="39" width="17.6666666666667" style="1" customWidth="1"/>
-    <col min="40" max="40" width="9.14166666666667" style="1"/>
-    <col min="41" max="16374" width="9.14166666666667" style="7"/>
-    <col min="16375" max="16384" width="9" style="7"/>
+    <col min="34" max="34" width="9.14166666666667" style="2"/>
+    <col min="35" max="36" width="18.25" style="2" customWidth="1"/>
+    <col min="37" max="37" width="9.14166666666667" style="2"/>
+    <col min="38" max="38" width="16.5" style="2" customWidth="1"/>
+    <col min="39" max="39" width="17.75" style="1" customWidth="1"/>
+    <col min="40" max="40" width="17.6666666666667" style="1" customWidth="1"/>
+    <col min="41" max="41" width="9.14166666666667" style="1"/>
+    <col min="42" max="16375" width="9.14166666666667" style="7"/>
+    <col min="16376" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40">
+    <row r="1" spans="1:41">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1471,7 +1532,7 @@
       <c r="AK1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" s="2" t="s">
         <v>37</v>
       </c>
       <c r="AM1" s="1" t="s">
@@ -1480,112 +1541,115 @@
       <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="2" spans="1:40">
+    <row r="2" spans="1:41">
       <c r="A2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="X2" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Y2" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Z2" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AA2" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AB2" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AC2" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AD2" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AE2" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AF2" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AG2" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ2" s="2" t="s">
         <v>75</v>
@@ -1593,7 +1657,7 @@
       <c r="AK2" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="AL2" s="1" t="s">
+      <c r="AL2" s="2" t="s">
         <v>77</v>
       </c>
       <c r="AM2" s="1" t="s">
@@ -1602,16 +1666,19 @@
       <c r="AN2" s="1" t="s">
         <v>79</v>
       </c>
+      <c r="AO2" s="1" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="3" ht="56" spans="1:40">
+    <row r="3" ht="42" spans="1:41">
       <c r="A3" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -1620,22 +1687,22 @@
         <v>1</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L3" s="3">
         <v>0</v>
@@ -1644,7 +1711,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O3" s="4">
         <v>100</v>
@@ -1665,16 +1732,16 @@
         <v>600</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="V3" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="W3" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="X3" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Y3" s="5">
         <v>0</v>
@@ -1695,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="AE3" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AF3" s="6">
         <v>550</v>
@@ -1709,31 +1776,2179 @@
       <c r="AI3" s="2">
         <v>100</v>
       </c>
-      <c r="AJ3" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK3" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AL3" s="1" t="s">
+      <c r="AJ3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL3" s="2" t="s">
         <v>93</v>
       </c>
       <c r="AM3" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN3" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:41">
+      <c r="A4" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="L4" s="3">
+        <v>20</v>
+      </c>
+      <c r="M4" s="3">
+        <v>20</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="O4" s="4">
+        <v>100</v>
+      </c>
+      <c r="P4" s="4">
+        <v>50</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>50</v>
+      </c>
+      <c r="R4" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="X4" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE4" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF4" s="6">
+        <v>550</v>
+      </c>
+      <c r="AG4" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="AH4" s="2">
+        <v>500</v>
+      </c>
+      <c r="AI4" s="2">
+        <v>50</v>
+      </c>
+      <c r="AJ4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="AN3" s="1">
+      <c r="AM4" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN4" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO4" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    <row r="5" spans="1:41">
+      <c r="A5" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="L5" s="3">
+        <v>30</v>
+      </c>
+      <c r="M5" s="3">
+        <v>20</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="O5" s="4">
+        <v>100</v>
+      </c>
+      <c r="P5" s="4">
+        <v>55</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>55</v>
+      </c>
+      <c r="R5" s="4">
+        <v>0.55</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="X5" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE5" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF5" s="6">
+        <v>550</v>
+      </c>
+      <c r="AG5" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="AH5" s="2">
+        <v>450</v>
+      </c>
+      <c r="AI5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM5" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN5" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:41">
+      <c r="A6" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="L6" s="3">
+        <v>25</v>
+      </c>
+      <c r="M6" s="3">
+        <v>20</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="O6" s="4">
+        <v>100</v>
+      </c>
+      <c r="P6" s="4">
+        <v>65</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>65</v>
+      </c>
+      <c r="R6" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="U6" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="X6" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE6" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>550</v>
+      </c>
+      <c r="AG6" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="AH6" s="2">
+        <v>600</v>
+      </c>
+      <c r="AI6" s="2">
+        <v>35</v>
+      </c>
+      <c r="AJ6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM6" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN6" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:41">
+      <c r="A7" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="3">
+        <v>30</v>
+      </c>
+      <c r="M7" s="3">
+        <v>20</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="O7" s="4">
+        <v>100</v>
+      </c>
+      <c r="P7" s="4">
+        <v>65</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>65</v>
+      </c>
+      <c r="R7" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="U7" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="X7" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE7" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF7" s="6">
+        <v>550</v>
+      </c>
+      <c r="AG7" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="AH7" s="2">
+        <v>700</v>
+      </c>
+      <c r="AI7" s="2">
+        <v>150</v>
+      </c>
+      <c r="AJ7" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM7" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN7" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:41">
+      <c r="A8" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="L8" s="3">
+        <v>20</v>
+      </c>
+      <c r="M8" s="3">
+        <v>20</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="O8" s="4">
+        <v>100</v>
+      </c>
+      <c r="P8" s="4">
+        <v>60</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>60</v>
+      </c>
+      <c r="R8" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="X8" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE8" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF8" s="6">
+        <v>550</v>
+      </c>
+      <c r="AG8" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="AH8" s="2">
+        <v>700</v>
+      </c>
+      <c r="AI8" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM8" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN8" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:41">
+      <c r="A9" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="L9" s="3">
+        <v>20</v>
+      </c>
+      <c r="M9" s="3">
+        <v>20</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="O9" s="4">
+        <v>100</v>
+      </c>
+      <c r="P9" s="4">
+        <v>75</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>75</v>
+      </c>
+      <c r="R9" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="U9" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="X9" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE9" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF9" s="6">
+        <v>550</v>
+      </c>
+      <c r="AG9" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="AH9" s="2">
+        <v>550</v>
+      </c>
+      <c r="AI9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM9" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN9" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:41">
+      <c r="A10" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="L10" s="3">
+        <v>20</v>
+      </c>
+      <c r="M10" s="3">
+        <v>20</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="O10" s="4">
+        <v>100</v>
+      </c>
+      <c r="P10" s="4">
+        <v>75</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>75</v>
+      </c>
+      <c r="R10" s="4">
+        <v>0.95</v>
+      </c>
+      <c r="U10" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="X10" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE10" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF10" s="6">
+        <v>550</v>
+      </c>
+      <c r="AG10" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="AH10" s="2">
+        <v>750</v>
+      </c>
+      <c r="AI10" s="2">
+        <v>150</v>
+      </c>
+      <c r="AJ10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM10" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN10" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:41">
+      <c r="A11" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+      <c r="L11" s="3">
+        <v>25</v>
+      </c>
+      <c r="M11" s="3">
+        <v>20</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="O11" s="4">
+        <v>100</v>
+      </c>
+      <c r="P11" s="4">
+        <v>40</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>40</v>
+      </c>
+      <c r="R11" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="U11" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="X11" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE11" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF11" s="6">
+        <v>550</v>
+      </c>
+      <c r="AG11" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="AH11" s="2">
+        <v>550</v>
+      </c>
+      <c r="AI11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM11" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN11" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:41">
+      <c r="A12" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="L12" s="3">
+        <v>20</v>
+      </c>
+      <c r="M12" s="3">
+        <v>20</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="O12" s="4">
+        <v>100</v>
+      </c>
+      <c r="P12" s="4">
+        <v>40</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>40</v>
+      </c>
+      <c r="R12" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="U12" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="X12" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE12" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF12" s="6">
+        <v>550</v>
+      </c>
+      <c r="AG12" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="AH12" s="2">
+        <v>500</v>
+      </c>
+      <c r="AI12" s="2">
+        <v>50</v>
+      </c>
+      <c r="AJ12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM12" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN12" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:41">
+      <c r="A13" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="L13" s="3">
+        <v>25</v>
+      </c>
+      <c r="M13" s="3">
+        <v>20</v>
+      </c>
+      <c r="N13" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="O13" s="4">
+        <v>100</v>
+      </c>
+      <c r="P13" s="4">
+        <v>60</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>60</v>
+      </c>
+      <c r="R13" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="U13" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="X13" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE13" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF13" s="6">
+        <v>550</v>
+      </c>
+      <c r="AG13" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="AH13" s="2">
+        <v>500</v>
+      </c>
+      <c r="AI13" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM13" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN13" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:41">
+      <c r="A14" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="L14" s="3">
+        <v>20</v>
+      </c>
+      <c r="M14" s="3">
+        <v>20</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="O14" s="4">
+        <v>100</v>
+      </c>
+      <c r="P14" s="4">
+        <v>65</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>65</v>
+      </c>
+      <c r="R14" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="U14" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="X14" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE14" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF14" s="6">
+        <v>550</v>
+      </c>
+      <c r="AG14" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="AH14" s="2">
+        <v>550</v>
+      </c>
+      <c r="AI14" s="2">
+        <v>125</v>
+      </c>
+      <c r="AJ14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM14" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN14" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:41">
+      <c r="A15" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="L15" s="3">
+        <v>20</v>
+      </c>
+      <c r="M15" s="3">
+        <v>20</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="O15" s="4">
+        <v>100</v>
+      </c>
+      <c r="P15" s="4">
+        <v>60</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>60</v>
+      </c>
+      <c r="R15" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="U15" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="X15" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE15" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF15" s="6">
+        <v>550</v>
+      </c>
+      <c r="AG15" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="AH15" s="2">
+        <v>600</v>
+      </c>
+      <c r="AI15" s="2">
+        <v>150</v>
+      </c>
+      <c r="AJ15" s="2">
+        <v>50</v>
+      </c>
+      <c r="AK15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM15" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN15" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:41">
+      <c r="A16" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1">
+        <v>1</v>
+      </c>
+      <c r="L16" s="3">
+        <v>20</v>
+      </c>
+      <c r="M16" s="3">
+        <v>20</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="O16" s="4">
+        <v>100</v>
+      </c>
+      <c r="P16" s="4">
+        <v>55</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>55</v>
+      </c>
+      <c r="R16" s="4">
+        <v>1.25</v>
+      </c>
+      <c r="U16" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="X16" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE16" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF16" s="6">
+        <v>550</v>
+      </c>
+      <c r="AG16" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="AH16" s="2">
+        <v>700</v>
+      </c>
+      <c r="AI16" s="2">
+        <v>125</v>
+      </c>
+      <c r="AJ16" s="2">
+        <v>50</v>
+      </c>
+      <c r="AK16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL16" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM16" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN16" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:41">
+      <c r="A17" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+      <c r="L17" s="3">
+        <v>20</v>
+      </c>
+      <c r="M17" s="3">
+        <v>20</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="O17" s="4">
+        <v>100</v>
+      </c>
+      <c r="P17" s="4">
+        <v>45</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>45</v>
+      </c>
+      <c r="R17" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="U17" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="X17" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE17" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF17" s="6">
+        <v>550</v>
+      </c>
+      <c r="AG17" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="AH17" s="2">
+        <v>500</v>
+      </c>
+      <c r="AI17" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL17" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM17" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN17" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO17" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:41">
+      <c r="A18" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
+        <v>1</v>
+      </c>
+      <c r="L18" s="3">
+        <v>30</v>
+      </c>
+      <c r="M18" s="3">
+        <v>20</v>
+      </c>
+      <c r="N18" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="O18" s="4">
+        <v>100</v>
+      </c>
+      <c r="P18" s="4">
+        <v>50</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>50</v>
+      </c>
+      <c r="R18" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="U18" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="X18" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE18" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF18" s="6">
+        <v>550</v>
+      </c>
+      <c r="AG18" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="AH18" s="2">
+        <v>650</v>
+      </c>
+      <c r="AI18" s="2">
+        <v>150</v>
+      </c>
+      <c r="AJ18" s="2">
+        <v>50</v>
+      </c>
+      <c r="AK18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL18" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM18" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN18" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:41">
+      <c r="A19" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="L19" s="3">
+        <v>20</v>
+      </c>
+      <c r="M19" s="3">
+        <v>20</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="O19" s="4">
+        <v>100</v>
+      </c>
+      <c r="P19" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q19" s="4">
+        <v>70</v>
+      </c>
+      <c r="R19" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="U19" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="X19" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE19" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF19" s="6">
+        <v>550</v>
+      </c>
+      <c r="AG19" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="AH19" s="2">
+        <v>550</v>
+      </c>
+      <c r="AI19" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ19" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL19" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM19" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN19" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:41">
+      <c r="A20" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1">
+        <v>1</v>
+      </c>
+      <c r="L20" s="3">
+        <v>25</v>
+      </c>
+      <c r="M20" s="3">
+        <v>20</v>
+      </c>
+      <c r="N20" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="O20" s="4">
+        <v>100</v>
+      </c>
+      <c r="P20" s="4">
+        <v>60</v>
+      </c>
+      <c r="Q20" s="4">
+        <v>60</v>
+      </c>
+      <c r="R20" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="U20" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="X20" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE20" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF20" s="6">
+        <v>550</v>
+      </c>
+      <c r="AG20" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="AH20" s="2">
+        <v>700</v>
+      </c>
+      <c r="AI20" s="2">
+        <v>150</v>
+      </c>
+      <c r="AJ20" s="2">
+        <v>50</v>
+      </c>
+      <c r="AK20" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM20" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN20" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:41">
+      <c r="A21" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1">
+        <v>1</v>
+      </c>
+      <c r="L21" s="3">
+        <v>25</v>
+      </c>
+      <c r="M21" s="3">
+        <v>20</v>
+      </c>
+      <c r="N21" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="O21" s="4">
+        <v>100</v>
+      </c>
+      <c r="P21" s="4">
+        <v>65</v>
+      </c>
+      <c r="Q21" s="4">
+        <v>65</v>
+      </c>
+      <c r="R21" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="U21" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="X21" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE21" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF21" s="6">
+        <v>550</v>
+      </c>
+      <c r="AG21" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="AH21" s="2">
+        <v>850</v>
+      </c>
+      <c r="AI21" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ21" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL21" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM21" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN21" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO21" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:41">
+      <c r="A22" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+      <c r="L22" s="3">
+        <v>40</v>
+      </c>
+      <c r="M22" s="3">
+        <v>20</v>
+      </c>
+      <c r="N22" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="O22" s="4">
+        <v>100</v>
+      </c>
+      <c r="P22" s="4">
+        <v>50</v>
+      </c>
+      <c r="Q22" s="4">
+        <v>50</v>
+      </c>
+      <c r="R22" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="U22" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="X22" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE22" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF22" s="6">
+        <v>550</v>
+      </c>
+      <c r="AG22" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="AH22" s="2">
+        <v>600</v>
+      </c>
+      <c r="AI22" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL22" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM22" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN22" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO22" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:41">
+      <c r="A23" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="L23" s="3">
+        <v>25</v>
+      </c>
+      <c r="M23" s="3">
+        <v>20</v>
+      </c>
+      <c r="N23" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="O23" s="4">
+        <v>100</v>
+      </c>
+      <c r="P23" s="4">
+        <v>40</v>
+      </c>
+      <c r="Q23" s="4">
+        <v>40</v>
+      </c>
+      <c r="R23" s="4">
+        <v>1</v>
+      </c>
+      <c r="U23" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="X23" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE23" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF23" s="6">
+        <v>550</v>
+      </c>
+      <c r="AG23" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="AH23" s="2">
+        <v>450</v>
+      </c>
+      <c r="AI23" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ23" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL23" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM23" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN23" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:41">
+      <c r="A24" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="L24" s="3">
+        <v>50</v>
+      </c>
+      <c r="M24" s="3">
+        <v>50</v>
+      </c>
+      <c r="N24" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="O24" s="4">
+        <v>100</v>
+      </c>
+      <c r="P24" s="4">
+        <v>55</v>
+      </c>
+      <c r="Q24" s="4">
+        <v>55</v>
+      </c>
+      <c r="R24" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="U24" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="X24" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE24" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF24" s="6">
+        <v>550</v>
+      </c>
+      <c r="AG24" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="AH24" s="2">
+        <v>800</v>
+      </c>
+      <c r="AI24" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ24" s="2">
+        <v>50</v>
+      </c>
+      <c r="AK24" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL24" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM24" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN24" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO24" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:41">
+      <c r="A25" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+      <c r="L25" s="3">
+        <v>75</v>
+      </c>
+      <c r="M25" s="3">
+        <v>20</v>
+      </c>
+      <c r="N25" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="O25" s="4">
+        <v>100</v>
+      </c>
+      <c r="P25" s="4">
+        <v>40</v>
+      </c>
+      <c r="Q25" s="4">
+        <v>40</v>
+      </c>
+      <c r="R25" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="U25" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="X25" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE25" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF25" s="6">
+        <v>550</v>
+      </c>
+      <c r="AG25" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="AH25" s="2">
+        <v>650</v>
+      </c>
+      <c r="AI25" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ25" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL25" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM25" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN25" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO25" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:41">
+      <c r="A26" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1</v>
+      </c>
+      <c r="L26" s="3">
+        <v>40</v>
+      </c>
+      <c r="M26" s="3">
+        <v>20</v>
+      </c>
+      <c r="N26" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="O26" s="4">
+        <v>100</v>
+      </c>
+      <c r="P26" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q26" s="4">
+        <v>70</v>
+      </c>
+      <c r="R26" s="4">
+        <v>1</v>
+      </c>
+      <c r="U26" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="X26" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE26" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF26" s="6">
+        <v>550</v>
+      </c>
+      <c r="AG26" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="AH26" s="2">
+        <v>750</v>
+      </c>
+      <c r="AI26" s="2">
+        <v>125</v>
+      </c>
+      <c r="AJ26" s="2">
+        <v>50</v>
+      </c>
+      <c r="AK26" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL26" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM26" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN26" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO26" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:41">
+      <c r="A27" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+      <c r="L27" s="3">
+        <v>20</v>
+      </c>
+      <c r="M27" s="3">
+        <v>20</v>
+      </c>
+      <c r="N27" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="O27" s="4">
+        <v>100</v>
+      </c>
+      <c r="P27" s="4">
+        <v>40</v>
+      </c>
+      <c r="Q27" s="4">
+        <v>40</v>
+      </c>
+      <c r="R27" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="U27" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="X27" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE27" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF27" s="6">
+        <v>550</v>
+      </c>
+      <c r="AG27" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="AH27" s="2">
+        <v>500</v>
+      </c>
+      <c r="AI27" s="2">
         <v>95</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="AJ27" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL27" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM27" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN27" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO27" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:41">
+      <c r="A28" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>96</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
+      <c r="L28" s="3">
+        <v>40</v>
+      </c>
+      <c r="M28" s="3">
+        <v>20</v>
+      </c>
+      <c r="N28" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="O28" s="4">
+        <v>100</v>
+      </c>
+      <c r="P28" s="4">
+        <v>50</v>
+      </c>
+      <c r="Q28" s="4">
+        <v>50</v>
+      </c>
+      <c r="R28" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="U28" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="X28" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE28" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF28" s="6">
+        <v>550</v>
+      </c>
+      <c r="AG28" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="AH28" s="2">
+        <v>700</v>
+      </c>
+      <c r="AI28" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ28" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM28" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN28" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO28" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:41">
+      <c r="A29" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1</v>
+      </c>
+      <c r="L29" s="3">
+        <v>20</v>
+      </c>
+      <c r="M29" s="3">
+        <v>20</v>
+      </c>
+      <c r="N29" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="O29" s="4">
+        <v>100</v>
+      </c>
+      <c r="P29" s="4">
+        <v>50</v>
+      </c>
+      <c r="Q29" s="4">
+        <v>50</v>
+      </c>
+      <c r="R29" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="U29" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="X29" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE29" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF29" s="6">
+        <v>550</v>
+      </c>
+      <c r="AG29" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="AH29" s="2">
+        <v>650</v>
+      </c>
+      <c r="AI29" s="2">
+        <v>150</v>
+      </c>
+      <c r="AJ29" s="2">
+        <v>50</v>
+      </c>
+      <c r="AK29" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM29" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN29" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO29" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:41">
+      <c r="A30" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+      <c r="E30" s="1">
+        <v>1</v>
+      </c>
+      <c r="L30" s="3">
+        <v>20</v>
+      </c>
+      <c r="M30" s="3">
+        <v>20</v>
+      </c>
+      <c r="N30" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="O30" s="4">
+        <v>100</v>
+      </c>
+      <c r="P30" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q30" s="4">
+        <v>70</v>
+      </c>
+      <c r="R30" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="U30" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="X30" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE30" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF30" s="6">
+        <v>550</v>
+      </c>
+      <c r="AG30" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="AH30" s="2">
+        <v>1000</v>
+      </c>
+      <c r="AI30" s="2">
+        <v>150</v>
+      </c>
+      <c r="AJ30" s="2">
+        <v>50</v>
+      </c>
+      <c r="AK30" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM30" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN30" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO30" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:41">
+      <c r="A31" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
+      <c r="E31" s="1">
+        <v>1</v>
+      </c>
+      <c r="L31" s="3">
+        <v>35</v>
+      </c>
+      <c r="M31" s="3">
+        <v>20</v>
+      </c>
+      <c r="N31" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="O31" s="4">
+        <v>100</v>
+      </c>
+      <c r="P31" s="4">
+        <v>75</v>
+      </c>
+      <c r="Q31" s="4">
+        <v>75</v>
+      </c>
+      <c r="R31" s="4">
+        <v>1</v>
+      </c>
+      <c r="U31" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="X31" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE31" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF31" s="6">
+        <v>550</v>
+      </c>
+      <c r="AG31" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="AH31" s="2">
+        <v>750</v>
+      </c>
+      <c r="AI31" s="2">
+        <v>25</v>
+      </c>
+      <c r="AJ31" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM31" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN31" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO31" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
